--- a/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JESUS_MARIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JESUS_MARIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JESUS_MARIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JESUS_MARIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JESUS_MARIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JESUS_MARIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JESUS_MARIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>127 TERESA GONZALES DE FANNING / TERESA GONZALES DE FANNING</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.07713</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.04575</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1839</v>
-      </c>
-      <c r="J2" t="n">
-        <v>128</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.07713</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.04575</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.08474</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.05859</v>
-      </c>
-      <c r="I3" t="n">
-        <v>308</v>
-      </c>
-      <c r="J3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.08474</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.05859</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.082632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.053735</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1323</v>
-      </c>
-      <c r="J4" t="n">
-        <v>109</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.082632</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.053735</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>SANTA MARIA DE FATIMA SRLDA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.0713</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.04991</v>
-      </c>
-      <c r="I5" t="n">
-        <v>103</v>
-      </c>
-      <c r="J5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.0713</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.04991</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>LOS ALAMITOS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.08488</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.05392000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>371</v>
-      </c>
-      <c r="J6" t="n">
-        <v>29</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.08488</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.05392</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>SACO OLIVEROS DE SALAVERRY</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.07396</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.04315</v>
-      </c>
-      <c r="I7" t="n">
-        <v>233</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.07396</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.04315</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>FANTASIA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.07393</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.04609000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>55</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.07393</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.04609</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>306661</t>
+          <t>307321</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>127 TERESA GONZALES DE FANNING / TERESA GONZALES DE FANNING</t>
+          <t>SACO OLIVEROS DE SALAVERRY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.07713</t>
+          <t>-12.07396</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.04575</t>
+          <t>-77.04315</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>306736</t>
+          <t>306779</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.08474</t>
+          <t>-12.082632</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.05859</t>
+          <t>-77.053735</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>306779</t>
+          <t>306661</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>127 TERESA GONZALES DE FANNING / TERESA GONZALES DE FANNING</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.082632</t>
+          <t>-12.07713</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.053735</t>
+          <t>-77.04575</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>307180</t>
+          <t>306736</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOS ALAMITOS</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.08488</t>
+          <t>-12.08474</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.05392</t>
+          <t>-77.05859</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>307321</t>
+          <t>307180</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE SALAVERRY</t>
+          <t>LOS ALAMITOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.07396</t>
+          <t>-12.08488</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.04315</t>
+          <t>-77.05392</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>371</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>307321</t>
+          <t>703892</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE SALAVERRY</t>
+          <t>FANTASIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.07396</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.04315</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-12.07393</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.04609</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>306779</t>
+          <t>307321</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>SACO OLIVEROS DE SALAVERRY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.082632</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.053735</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>-12.07396</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>-77.04315</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>306661</t>
+          <t>307180</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>127 TERESA GONZALES DE FANNING / TERESA GONZALES DE FANNING</t>
+          <t>LOS ALAMITOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.07713</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.04575</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>-12.08488</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>-77.05392</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -697,22 +697,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>-12.0713</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-77.04991</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>306736</t>
+          <t>306779</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -759,22 +759,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.08474</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.05859</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-12.082632</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.053735</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>307180</t>
+          <t>306736</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LOS ALAMITOS</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.08488</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.05392</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>-12.08474</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.05859</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>703892</t>
+          <t>306661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FANTASIA</t>
+          <t>127 TERESA GONZALES DE FANNING / TERESA GONZALES DE FANNING</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.07393</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.04609</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-12.07713</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.04575</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-JESUS_MARIA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
